--- a/www/download/COUNTRY.BGR.EXI382.xlsx
+++ b/www/download/COUNTRY.BGR.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2697</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.876</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2.894</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2.757</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.819</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.597</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.716</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.714</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.894</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.96</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.011</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>3.122</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3.236</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3.353</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>3.209</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3.044</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.958</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.927</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.786</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2.972</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3.133</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>3.486</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>3.809</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>4.114</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4.327</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.343</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.767</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2.688</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2.553</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2.414</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.473</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.264</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.378</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.374</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.524</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.581</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.832</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.936</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.806</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.655</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.587</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.471</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2.635</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2.784</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2.879</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3.082</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>3.393</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>3.673</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3.865</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10227.209</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>6573.78</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>6410.759</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>6100.288</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5815.83</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5950.544</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5485.504</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>5824.643</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>5819.111</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6017.383</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6274.409</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6377.546</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6687.298</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6946.884</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>7178.934</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6758.883</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>6426.469</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>6201.404</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>6119.407</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>5812.36</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>6194.427</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6550.217</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>6758.492</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7317.713</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>7982.493</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>8616.463</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>9054.641</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9006.52</t>
+          <t>9917885874.86298</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5031.493</t>
+          <t>9613847124.33142</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4868.873</t>
+          <t>9530886731.65303</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4614.069</t>
+          <t>8650662802.59483</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4315.225</t>
+          <t>8518779970.18503</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4439.533</t>
+          <t>8388255277.5326</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4747.225</t>
+          <t>7604465922.82085</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5044.654</t>
+          <t>7336172565.05747</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5019.456</t>
+          <t>7371242326.86699</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5203.97</t>
+          <t>8254322227.61018</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5396.679</t>
+          <t>8452995720.92208</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5520.402</t>
+          <t>8664675725.53171</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5761.686</t>
+          <t>9044033294.92558</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5980.152</t>
+          <t>10004517222.2994</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6188.919</t>
+          <t>9585683786.10839</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5827.952</t>
+          <t>8404888180.12501</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5524.659</t>
+          <t>8287754181.90252</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5397.443</t>
+          <t>7989147118.2612</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5343.615</t>
+          <t>7745799581.96652</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5089.079</t>
+          <t>11038114608.5164</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>5424.965</t>
+          <t>10482786190.9328</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5741.981</t>
+          <t>11599126834.784</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>5950.278</t>
+          <t>10786875607.2786</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6391.345</t>
+          <t>11655305335.7584</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>7029.369</t>
+          <t>12569573048.1793</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>7600.424</t>
+          <t>12988934444.1443</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>7992.322</t>
+          <t>11074572190.2238</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1326190490.38306</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1159094823.8967</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1300400494.09145</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1152718023.2577</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1150147205.68157</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1198473346.21971</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1075264350.1726</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1067836317.02445</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1045612701.95462</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1134888558.37428</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1139206260.29887</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1337242339.6059</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1204585607.86334</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1416142077.98316</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1728852436.92357</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1586499497.67271</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1548895971.54588</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1442935471.41064</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1537970077.94297</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1483316071.23207</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1611857198.32161</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1758960637.60183</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1476779827.44905</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2150869109.47585</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2256412751.23517</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2680789603.30148</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1722965421.57162</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>75697649.6892674</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>121165127.176041</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>74820095.792027</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>55119292.5111839</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>53489859.6714749</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>45542775.6876039</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35903207.4902502</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>31482885.0614879</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>29220597.2148452</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>29892209.2453798</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>24297803.4747005</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>22431126.5540919</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>17493498.2042581</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>20244781.6677139</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>16192186.0610757</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>14904612.6948075</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>14043727.1985245</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>12378251.8097153</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>11709184.451043</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>14598213.5323324</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>20531800.8297237</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>13798660.2910909</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>17239068.915723</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12972197.6469019</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>13501357.3155634</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15653051.7002822</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>13654978.2866094</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>19349.5786721656</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>36451.7349318547</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>38314.3542995899</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>37211.9755547703</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>36236.075602707</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>43462.3437310514</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>38583.3046306414</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>40045.6092746636</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>36318.2797738633</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>36122.4793876889</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>39575.1268778429</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>42535.247407354</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>45829.8361908341</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>47670.8541326941</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>49139.7578213933</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>51886.4418964086</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>50178.6597412565</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>52302.5417312481</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>50248.9552423921</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>49733.0365568036</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>58711.2177145734</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>55228.0078103374</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>60155.1037504975</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>68873.5388746144</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>72780.6969838321</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>75154.0313331296</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>78291.5411915633</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>36969.9375855968</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>73056.32062516</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>78883.5660441412</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>73607.9795788076</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>76458.5619648459</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>89996.0262072142</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>81921.0215402314</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76608.9849362914</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>70710.7174030152</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>77379.4981396798</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>84950.6778237946</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>93147.9492445969</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>100731.648314298</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>111965.649823167</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>107504.872907246</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>108703.442374196</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>111588.897884436</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>118729.504460702</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>112445.611797015</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>165861.346428365</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>177936.355230558</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>179455.169015716</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>176441.902127037</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>185417.896903137</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>213052.638377924</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>209439.515170996</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>175317.788773849</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5.79127152825271</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.34088122582201</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2.74413373581596</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3.00277353776523</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.75188947874185</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.70432374987994</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.41493766554986</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3.7241824983602</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3.8004925634671</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3.58544599960957</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3.73722737319327</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3.12819875388243</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3.7831268798066</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3.2228473632497</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2.57978431693872</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.67346602287086</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2.56683696096444</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.74059934552863</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.47445976786904</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.43087939596005</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2.36566078345649</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2.26441683862562</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>3.02922464942478</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.97151749692834</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2.11528509503771</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.83514362594031</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3.63870115304961</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>305.350293717324</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>418.914606200767</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>483.851947496345</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>451.444357819879</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>476.42898209748</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>484.564487211418</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>474.835217563606</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>448.972551725648</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>440.499095064648</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>449.603263756418</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>441.347536145487</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>508.360516862328</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>441.320977418281</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>500.067826541537</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>588.745934590092</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>565.455856888607</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>583.432262899534</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>554.953836933617</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>594.407543457935</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>600.293623759795</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>611.820955321798</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>631.773569448376</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>512.911853117967</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>697.980915589984</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>664.98838624314</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>729.845623949154</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>445.74847152994</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>715770291.234734</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-288847408.981354</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-591239889.068669</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-388730044.862016</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-200455910.127368</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-118331812.639902</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>419746825.055634</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-73123740.8780855</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-20607304.3482785</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>14875940.9699342</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>-214029937.122401</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-90792461.0038875</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-374673168.215479</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-64784077.1848662</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>83347669.2088334</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>181299308.245513</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>402796636.966114</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>313382038.838718</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>424992259.486957</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>558532862.875907</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>598000922.489921</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1016884059.57169</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>721931247.114872</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>696338743.85351</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>767124478.17443</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1056948249.45234</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>16064330.212223</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>517492362.431797</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-408599268.759919</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-660967529.350381</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-460700018.66583</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-209759630.645924</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-144325201.153146</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>357567758.869668</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-48164679.04203</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-83960722.4922364</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-18681544.1388094</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-120199704.296364</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-78967704.5402957</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-414512511.012159</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-181444845.097676</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-104011218.627615</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-133361816.479576</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>31044982.6669902</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-18200311.4968098</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>65245250.0706459</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>173880370.524303</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>158462116.177003</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>468522682.048393</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>244479420.507026</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>178108909.050621</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>233864437.726672</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>443358932.169788</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>557620930.92971</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>198277928.802937</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>119751859.778566</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>69727640.2817113</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>71969973.8038137</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>9303720.51855649</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>25993388.5132445</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>62179066.185966</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-24959061.8360555</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>63353418.1439578</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>33557485.1087436</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-93830232.8260375</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-11824756.4635918</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>39839342.7966805</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>116660767.91281</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>187358887.836449</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>314661124.725089</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>371751654.299124</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>331582350.335528</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>359747009.416311</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>384652492.351603</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>439538806.312919</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>548361377.5233</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>477451826.607846</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>518229834.802888</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>533260040.447757</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>613589317.282556</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-541556600.717487</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2073.71675586606</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1818.45854927953</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1811.60639976132</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1807.02952925483</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1787.50888529922</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1794.98373832565</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>2096.36788695112</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>2121.02827110642</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2114.61263007183</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>2061.63148720327</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2090.76362931981</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2098.61325223409</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>2110.8942297119</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>2111.71010275694</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>2107.58346330704</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2077.18287771363</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>2081.00775952918</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>2075.85995923249</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>2065.24509546246</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2059.53502528367</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>2059.18179582346</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>2062.37227830589</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>2066.63708156505</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>2074.0625031977</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>2071.62840803643</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2069.21716865987</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>2067.69394885603</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2097.515820844</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2107.11573818901</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2108.52474674341</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2107.83610794347</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2109.47760609378</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2110.49621564124</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2111.92132132174</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2144.64550241136</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2143.71393626864</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2079.11800151977</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2120.09104240593</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2118.08227167116</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2142.06037348986</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2146.81660125399</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2140.98411619145</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>2106.09576218382</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2111.05343932689</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>2096.27269715732</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2090.67536727009</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>2086.11023346857</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2084.00351951147</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>2090.91962936724</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2092.64779090276</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2099.34292575468</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>2095.47547250989</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2094.27064155325</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2092.59384037061</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5366.28467455011</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5422.46494089356</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>5726.48627732672</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6464.56352421029</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6201.64747043665</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5764.28780956629</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6004.15329750404</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6133.52193858413</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>6510.43823023074</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>8735.12996118707</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10071.5138898179</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>12838.084614791</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>17439.406256965</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>22037.6956522616</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>18044.6028106548</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>22436.5124868838</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>28700.9999997727</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>30101.970586754</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>32076.1717488284</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>32611.1395582666</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>34903.3233121238</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>37277.9923478853</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>41929.8827257198</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>43945.2633437863</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>46111.9391111898</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>48056.7824448371</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>48201.0042200459</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2318159646.82337</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2966485180.60963</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2489272275.50249</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2271435998.64905</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2044634877.25941</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1651480968.67008</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1175026213.25642</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1246144947.51483</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1318587909.64949</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1647553750.87797</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1598422532.28817</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1740801309.93515</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2110485126.27865</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2431798354.93964</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2225409958.06064</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2360095761.93464</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2700848308.81803</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2583589392.55387</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2830735695.10032</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>4915124217.4316</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>4632347914.20865</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>4839382199.74096</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>4739486210.95892</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>5257606964.02545</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>5912167708.95745</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>5655571676.41008</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>4280145583.6216</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3578.30641882319</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4007.12911006253</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4070.33012317583</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5265.4861702655</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6967.38083904665</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6760.03680847259</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7934.44174343118</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>7943.02232807751</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8999.40143763183</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>11802.1852517186</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>14673.5970877787</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>18959.5297548489</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>25421.0458526278</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>31598.594402865</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>22071.8874184553</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>23859.3920186416</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>28498.0315604857</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>31853.8814019222</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>32320.2551068202</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>33159.5318154242</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>34332.577200827</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>34130.3102088603</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>38970.625041694</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>42048.6623594545</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>43393.9661289214</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>45706.6190771043</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>46053.1066701099</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10227.209</t>
+          <t>2020993340.17864</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6573.78</t>
+          <t>2390129212.5326</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6410.759</t>
+          <t>1588020296.63374</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6100.288</t>
+          <t>1656801794.12247</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5815.83</t>
+          <t>1984648077.1598</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5950.544</t>
+          <t>1687630231.64278</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5485.504</t>
+          <t>1906088006.49665</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5824.643</t>
+          <t>1475811331.89066</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5819.111</t>
+          <t>1720799843.56643</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6017.383</t>
+          <t>2224896475.9093</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6274.409</t>
+          <t>2154093699.09885</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6377.546</t>
+          <t>2560829075.29251</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6687.298</t>
+          <t>2726991151.05824</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6946.884</t>
+          <t>3677233622.66759</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7178.934</t>
+          <t>2901539327.09993</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6758.883</t>
+          <t>2716838985.51848</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6426.469</t>
+          <t>3080239486.90429</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6201.404</t>
+          <t>3087984425.12731</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>6119.407</t>
+          <t>3283688571.4029</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>5812.36</t>
+          <t>5531954518.34598</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>6194.427</t>
+          <t>5175177730.39779</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>6550.217</t>
+          <t>5522434008.62451</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>6758.492</t>
+          <t>5176373599.20674</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7317.713</t>
+          <t>5765443093.35313</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>7982.493</t>
+          <t>6431229843.19695</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>8616.463</t>
+          <t>6484456955.3371</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>9054.641</t>
+          <t>4086929357.14163</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9006.52</t>
+          <t>1787.97825572693</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5031.493</t>
+          <t>1415.33583083103</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4868.873</t>
+          <t>1656.15615415089</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4614.069</t>
+          <t>1199.07735394479</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4315.225</t>
+          <t>-765.733368609999</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4439.533</t>
+          <t>-995.748998906293</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4747.225</t>
+          <t>-1930.28844592714</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5044.654</t>
+          <t>-1809.50038949338</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5019.456</t>
+          <t>-2488.96320740109</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5203.97</t>
+          <t>-3067.0552905315</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5396.679</t>
+          <t>-4602.08319796074</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5520.402</t>
+          <t>-6121.44514005788</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5761.686</t>
+          <t>-7981.63959566278</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5980.152</t>
+          <t>-9560.89875060346</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6188.919</t>
+          <t>-4027.28460780054</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>5827.952</t>
+          <t>-1422.8795317578</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5524.659</t>
+          <t>202.968439286934</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5397.443</t>
+          <t>-1751.91081516828</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5343.615</t>
+          <t>-244.083357991842</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>5089.079</t>
+          <t>-548.392257157666</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>5424.965</t>
+          <t>570.746111296828</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>5741.981</t>
+          <t>3147.68213902507</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>5950.278</t>
+          <t>2959.25768402586</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6391.345</t>
+          <t>1896.60098433173</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>7029.369</t>
+          <t>2717.9729822684</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>7600.424</t>
+          <t>2350.16336773282</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>7992.322</t>
+          <t>2147.89754993602</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9027.24</t>
+          <t>297166306.644731</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8704.588</t>
+          <t>576355968.077027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8681.275</t>
+          <t>901251978.868756</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7919.29</t>
+          <t>614634204.52658</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7722.532</t>
+          <t>59986800.0996024</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7638.098</t>
+          <t>-36149262.9726979</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6838.202</t>
+          <t>-731061793.240228</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6720.236</t>
+          <t>-229666384.375837</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6716.743</t>
+          <t>-402211933.916939</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7399.785</t>
+          <t>-577342725.031325</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7579.107</t>
+          <t>-555671166.810684</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7725.147</t>
+          <t>-820027765.357358</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>8058.756</t>
+          <t>-616506024.779591</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>8826.623</t>
+          <t>-1245435267.72796</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8574.505</t>
+          <t>-676129369.039294</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>7481.846</t>
+          <t>-356743223.58384</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>7308.209</t>
+          <t>-379391178.086262</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>7017.167</t>
+          <t>-504395032.573437</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>6807.452</t>
+          <t>-452952876.30258</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>9459.128</t>
+          <t>-616830300.914383</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>9080.846</t>
+          <t>-542829816.189145</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>10008.398</t>
+          <t>-683051808.883551</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>9339.401</t>
+          <t>-436887388.247818</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10186.696</t>
+          <t>-507836129.327685</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>10895.263</t>
+          <t>-519062134.239505</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11282.095</t>
+          <t>-828885278.92702</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>9850.215</t>
+          <t>193216226.479974</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>4204.86877948635</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2604.71195692978</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>3263.73184670381</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>4806.74551484607</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>4325.50032311484</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>4919.94623181168</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>5505.19771291803</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>5925.36812320347</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>6601.27657787216</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>7390.64719020411</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>8569.51205469795</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>10009.7865663099</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>12051.7181354321</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>13885.0527676243</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>13119.1380030318</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>12916.8438553234</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>14521.7315364906</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>14639.0873034467</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>14784.2609391427</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>14701.7537460543</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>15580.0126450007</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>16763.7486539851</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>18697.6743651553</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>18889.0971777982</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>20630.1204830157</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>22484.2741697168</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>20318.3779142493</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>5190.891</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>4796.866</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>4629.225</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>4373.279</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>4037.313</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>4050.993</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3581.565</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3834.818</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>3786.001</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>3853.302</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>3937.913</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>3956.653</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>4114.76</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>4259.555</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>4381.552</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>4011.83</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>3726.79</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>3519.367</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>3461.392</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>3309.746</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>3458.861</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>3569.675</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>3677.616</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>4329.367</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>4293.879</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>4660.872</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>4945.564</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>6849.35756134678</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>3912.50230921894</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>4680.81455265754</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>6745.56938840025</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>6605.33303147635</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>7437.2696985272</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>7672.11085667238</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>7883.67058111154</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>8917.42504960623</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>9569.59773883571</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>11869.1940357693</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>14633.5672815863</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>16674.6767967814</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>19627.1183082369</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>20359.8862011246</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>21273.3593112703</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>23292.9559817037</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>23612.7538313717</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>23275.7153413398</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>24554.8061918618</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>26108.3621508289</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>27915.4844392295</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>27263.8150900026</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>33310.919240621</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>35361.8982483466</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>38056.9464699534</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>38208.4951236881</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1196.665</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1040.344</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1186.33</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1045.478</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1035.427</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1087.548</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>961.129</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>972.716</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>947.512</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1023.25</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1037.583</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1222.255</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1094.46</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1270.973</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1558.753</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1416.309</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1368.12</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1280.918</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1360.221</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1297.616</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>1413.938</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1544.697</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>1291.301</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>1899.752</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2003.483</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>2376.632</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1522.653</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>652.63</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>383.64</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>310.41</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>341.34</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>316.76</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>308.22</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>393.92</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>418.62</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>429.75</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>408.57</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>420.12</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>351.66</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>426.44</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>370.52</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>297.04</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>311.49</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>303.81</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>321.37</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>292.85</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>292.19</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>283.68</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>271.72</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>360.8</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>236.43</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>250.86</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>219.8</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>424.89</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>91.261</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>144.787</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>88.646</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>65.906</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>63.477</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>53.989</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>42.152</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>37.531</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>34.734</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>34.727</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>28.357</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>26.266</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>20.332</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>23.701</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>18.768</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>17.268</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>16.334</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>14.294</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>13.526</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>16.907</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>24.775</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>16.068</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>20.689</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15.322</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>15.989</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>18.654</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>16.409</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>11023.1694739865</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8018.92011933701</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>7274.90479259744</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>9422.4508033083</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>8982.19664872653</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>9931.00631078062</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11163.6950641903</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>12908.1765277245</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>13150.0412555426</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>15004.3419238992</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>16687.594599835</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>17910.8010193943</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>21777.7259677096</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>23854.5660911268</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>24548.4828003909</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>24660.6109358181</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>26345.2936963352</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>26802.5940329534</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>26877.933111197</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>26616.4278630926</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>28392.7492933627</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>29721.3174939352</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>34469.8055987696</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>33560.9648182724</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>36547.2636146458</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>36343.5598583484</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>38861.7204760824</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>9006519718.378</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5031492960.00066</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4868873359.99955</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4614069200.00096</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4315225200.00101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4439533279.99975</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4747225080.00001</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5044653640.00032</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5019455999.99992</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5203970200</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5396679080.00092</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5520402159.9999</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5761685799.9993</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5980151839.99816</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6188918840.00027</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5827952000.00237</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5524659399.99879</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5397443479.99868</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5343615159.99926</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>5089078546.48653</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>5424964560.92309</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>5741980723.86705</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>5950277682.53099</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>6391345192.41017</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>7029369012.17596</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>7600423556.28724</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>7992321687.70886</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10227209464.5633</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6573779680.00082</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6410758639.99939</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6100288480.00096</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>5815829760.00081</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5950544079.99921</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5485504440.0003</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5824642719.99998</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5819111479.99978</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6017383319.9998</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6274409440.00117</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6377545719.99984</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6687298279.99894</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6946883839.99818</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7178933840.00061</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6758882520.00165</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6426468879.99931</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>6201403519.99875</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>6119406799.99922</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>5812360247.23949</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>6194426501.58921</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>6550216728.36806</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>6758491846.82007</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>7317713470.79959</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>7982492683.94338</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>8616463156.35127</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>9054640595.91263</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5190890911.10576</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4796866363.5493</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4629224936.68041</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4373279290.97785</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4037313115.88595</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4050992577.56676</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3581564532.97444</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3834817813.55162</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3786000919.52514</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3853302123.87734</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3937912995.19983</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3956653138.14049</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4114760071.40903</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4259555336.17221</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4381551896.79849</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4011830101.04368</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3726790074.97272</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3519367005.26062</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3461391959.10451</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3309746177.54372</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>3458861127.69767</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3569675206.00338</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>3677616334.19911</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>4329367005.80317</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>4293879175.59098</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>4660872068.01544</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>4945563886.4365</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4875867.61583906</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3119799.99999941</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3040400.00000034</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2894100.00000083</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2757000.00000012</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2819499.9999994</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2597399.99999963</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2715900.00000045</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2714499.99999933</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2894200.00000061</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2959500.00000039</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3010999.99999905</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3121900.00000044</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3235900.00000019</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3353099.99999957</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>3209200.00000063</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3044200.00000018</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2958299.99999917</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2926999.99999984</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2786219.13357632</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2972368.54141268</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>3132696.55914527</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>3229636.57630341</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>3485716.1167078</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>3809394.4733136</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>4114302.60511159</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4326993.81085294</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4343177.3856775</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2766899.99999952</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2687600.00000056</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2553400.00000093</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2414100.00000008</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2473299.9999994</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2264499.99999961</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2378400.00000038</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2373699.99999925</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2524200.00000073</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2581200.0000003</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2630499.9999991</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2729500.00000031</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2831900.00000037</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2936499.99999959</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2805700.0000006</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2654800.00000034</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2600099.99999917</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2587399.99999985</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2470984.2192587</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2634524.3396801</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2784163.06515899</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2879207.83751004</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>3081558.62350159</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>3393161.14072728</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>3673091.28853288</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3865331.08158036</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10227209464.5633</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6573779680.00082</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6410758639.99939</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6100288480.00096</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5815829760.00081</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5950544079.99921</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5485504440.0003</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5824642719.99998</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5819111479.99978</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6017383319.9998</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6274409440.00117</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6377545719.99984</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6687298279.99894</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6946883839.99818</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7178933840.00061</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6758882520.00165</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6426468879.99931</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>6201403519.99875</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>6119406799.99922</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>5812360247.23949</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>6194426501.58921</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>6550216728.36806</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>6758491846.82007</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>7317713470.79959</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>7982492683.94338</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>8616463156.35127</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>9054640595.91263</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>9006519718.378</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5031492960.00066</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4868873359.99955</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4614069200.00096</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4315225200.00101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4439533279.99975</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4747225080.00001</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5044653640.00032</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5019455999.99992</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5203970200</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5396679080.00092</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5520402159.9999</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5761685799.9993</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5980151839.99816</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6188918840.00027</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>5827952000.00237</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5524659399.99879</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5397443479.99868</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5343615159.99926</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>5089078546.48653</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>5424964560.92309</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>5741980723.86705</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>5950277682.53099</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>6391345192.41017</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>7029369012.17596</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>7600423556.28724</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>7992321687.70886</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>33387.2194725734</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>23327.4193130702</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>26774.9782913088</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>33286.7399093646</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>32033.5873647222</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>36023.8725266684</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40082.5911395038</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>43120.0127263647</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>46911.0185226137</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>54035.9953206914</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>66215.381638042</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>75665.5277696344</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>90942.4769604698</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>106888.029932355</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>97564.0930546447</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>99100.5890313891</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>107343.239373393</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>112114.194796552</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>108211.068869786</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>114363.579815011</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>121625.857069346</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>127578.161250142</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>139558.393637725</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>146936.398467091</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>157268.448327749</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>165375.931556104</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>169115.811890214</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7412.59685507332</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4275.84851873013</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5395.39324198548</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>7600.9187182648</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>7263.81201336957</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8278.65784178765</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8944.30587964316</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9116.92651824268</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>10583.8256687442</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>11695.9482368203</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>13795.6419466615</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>16855.8023622092</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>19359.9562950984</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>23140.4394916659</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>22787.1266028911</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>23575.4974033476</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>25979.9344588617</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>26574.6366105645</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>26270.1146722125</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>27749.7023691494</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>29548.4807157118</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>31972.8656272604</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>31787.3777960546</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>37610.160654865</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>40491.6783114033</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>43160.6282093114</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>43027.5932335813</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
